--- a/poules_senior_masculin.xlsx
+++ b/poules_senior_masculin.xlsx
@@ -419,7 +419,7 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>Distance moyenne : 40 km ---- Écart-type : 10</v>
+        <v>Distance moyenne : 26 km ---- Écart-type : 10</v>
       </c>
     </row>
     <row r="4">
@@ -441,7 +441,7 @@
         <v>PDL0049170</v>
       </c>
       <c r="C5" t="str">
-        <v>334</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>PDL0049126</v>
       </c>
       <c r="C6" t="str">
-        <v>208</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7">
@@ -463,7 +463,7 @@
         <v>PDL0049152</v>
       </c>
       <c r="C7" t="str">
-        <v>211</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -474,7 +474,7 @@
         <v>PDL0049084</v>
       </c>
       <c r="C8" t="str">
-        <v>159</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9">
@@ -485,7 +485,7 @@
         <v>PDL0049115</v>
       </c>
       <c r="C9" t="str">
-        <v>146</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v>PDL0049031</v>
       </c>
       <c r="C10" t="str">
-        <v>137</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +793,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <cols>
     <col min="1" max="1" width="56.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -813,7 +813,7 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>Distance moyenne : 35 km ---- Écart-type : 8</v>
+        <v>Distance moyenne : 36 km ---- Écart-type : 9</v>
       </c>
     </row>
     <row r="4">
@@ -835,62 +835,62 @@
         <v>PDL0049067</v>
       </c>
       <c r="C5" t="str">
-        <v>266</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ETOILE ANGERS BASKET-2</v>
+        <v>CTC LOIRE ET PLAINE BASKET​-1</v>
       </c>
       <c r="B6" t="str">
         <v>PDL0049095</v>
       </c>
       <c r="C6" t="str">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AVRILLE BASKET-1</v>
+        <v>CANDE LOIRE BASKET-1</v>
       </c>
       <c r="B7" t="str">
-        <v>PDL0049012</v>
+        <v>PDL0049077</v>
       </c>
       <c r="C7" t="str">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CANDE LOIRE BASKET-1</v>
+        <v>AVRILLE BASKET-1</v>
       </c>
       <c r="B8" t="str">
-        <v>PDL0049077</v>
+        <v>PDL0049012</v>
       </c>
       <c r="C8" t="str">
-        <v>165</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MURS ERIGNE BASKET-1</v>
+        <v>SAINT MARTIN DU BOIS-1</v>
       </c>
       <c r="B9" t="str">
-        <v>PDL0049082</v>
+        <v>PDL0049110</v>
       </c>
       <c r="C9" t="str">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SAINT MARTIN DU BOIS-1</v>
+        <v>Exempt</v>
       </c>
       <c r="B10" t="str">
-        <v>PDL0049110</v>
+        <v>—</v>
       </c>
       <c r="C10" t="str">
-        <v>169</v>
+        <v>—</v>
       </c>
     </row>
     <row r="12">
@@ -901,7 +901,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Distance moyenne : 20 km ---- Écart-type : 5</v>
+        <v>Distance moyenne : 19 km ---- Écart-type : 6</v>
       </c>
     </row>
     <row r="13">
@@ -923,7 +923,7 @@
         <v>PDL0049149</v>
       </c>
       <c r="C14" t="str">
-        <v>83</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -934,7 +934,7 @@
         <v>PDL0049054</v>
       </c>
       <c r="C15" t="str">
-        <v>98</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
@@ -945,18 +945,18 @@
         <v>PDL0049024</v>
       </c>
       <c r="C16" t="str">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CTC LOIRE ET PLAINE BASKET​-1</v>
+        <v>ETOILE ANGERS BASKET-1</v>
       </c>
       <c r="B17" t="str">
         <v>PDL0049095</v>
       </c>
       <c r="C17" t="str">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
@@ -967,166 +967,199 @@
         <v>PDL0049053</v>
       </c>
       <c r="C18" t="str">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Poule C</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v>Distance moyenne : 15 km ---- Écart-type : 3</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>MURS ERIGNE BASKET-1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>PDL0049082</v>
+      </c>
+      <c r="C19" t="str">
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Équipe</v>
+        <v>Poule C</v>
       </c>
       <c r="B21" t="str">
-        <v>Numéro Club</v>
+        <v/>
       </c>
       <c r="C21" t="str">
-        <v>Distance totale (km)</v>
+        <v>Distance moyenne : 15 km ---- Écart-type : 3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ETRICHE BASKET-1</v>
+        <v>Équipe</v>
       </c>
       <c r="B22" t="str">
-        <v>PDL0049055</v>
+        <v>Numéro Club</v>
       </c>
       <c r="C22" t="str">
-        <v>75</v>
+        <v>Distance totale (km)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CHAMPIGNE-3</v>
+        <v>ETRICHE BASKET-1</v>
       </c>
       <c r="B23" t="str">
-        <v>PDL0049033</v>
+        <v>PDL0049055</v>
       </c>
       <c r="C23" t="str">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FENEU - REBOND FANOUIN-1</v>
+        <v>CHAMPIGNE-3</v>
       </c>
       <c r="B24" t="str">
-        <v>PDL0049198</v>
+        <v>PDL0049033</v>
       </c>
       <c r="C24" t="str">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CTC LOIRE ET PLAINE BASKET​-2</v>
+        <v>FENEU - REBOND FANOUIN-1</v>
       </c>
       <c r="B25" t="str">
-        <v>PDL0049095</v>
+        <v>PDL0049198</v>
       </c>
       <c r="C25" t="str">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
+        <v>CTC LOIRE ET PLAINE BASKET​-2</v>
+      </c>
+      <c r="B26" t="str">
+        <v>PDL0049095</v>
+      </c>
+      <c r="C26" t="str">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
         <v>ANGERS ALJF-2</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B27" t="str">
         <v>PDL0049006</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C27" t="str">
         <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Poule D</v>
+        <v>Exempt</v>
       </c>
       <c r="B28" t="str">
-        <v/>
+        <v>—</v>
       </c>
       <c r="C28" t="str">
-        <v>Distance moyenne : 28 km ---- Écart-type : 13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Équipe</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Numéro Club</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Distance totale (km)</v>
+        <v>—</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>YZERNAY-8</v>
+        <v>Poule D</v>
       </c>
       <c r="B30" t="str">
-        <v>PDL0049138</v>
+        <v/>
       </c>
       <c r="C30" t="str">
-        <v>100</v>
+        <v>Distance moyenne : 28 km ---- Écart-type : 13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SAINT CHRISTOPHE DU BOIS - ESSOR CHRISTOPHORIEN BASKET-1</v>
+        <v>Équipe</v>
       </c>
       <c r="B31" t="str">
-        <v>PDL0049097</v>
+        <v>Numéro Club</v>
       </c>
       <c r="C31" t="str">
-        <v>116</v>
+        <v>Distance totale (km)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>AVENIR TREMENTINES-2</v>
+        <v>YZERNAY-8</v>
       </c>
       <c r="B32" t="str">
-        <v>PDL0049131</v>
+        <v>PDL0049138</v>
       </c>
       <c r="C32" t="str">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TOURMELAY-1</v>
+        <v>SAINT CHRISTOPHE DU BOIS - ESSOR CHRISTOPHORIEN BASKET-1</v>
       </c>
       <c r="B33" t="str">
-        <v>PDL0049128</v>
+        <v>PDL0049097</v>
       </c>
       <c r="C33" t="str">
-        <v>83</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ETOILE ANGERS BASKET-1</v>
+        <v>AVENIR TREMENTINES-2</v>
       </c>
       <c r="B34" t="str">
+        <v>PDL0049131</v>
+      </c>
+      <c r="C34" t="str">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TOURMELAY-1</v>
+      </c>
+      <c r="B35" t="str">
+        <v>PDL0049128</v>
+      </c>
+      <c r="C35" t="str">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>ETOILE ANGERS BASKET-2</v>
+      </c>
+      <c r="B36" t="str">
         <v>PDL0049095</v>
       </c>
-      <c r="C34" t="str">
+      <c r="C36" t="str">
         <v>186</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Exempt</v>
+      </c>
+      <c r="B37" t="str">
+        <v>—</v>
+      </c>
+      <c r="C37" t="str">
+        <v>—</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C37"/>
   </ignoredErrors>
 </worksheet>
 </file>